--- a/public/downloads/BajdichWO32018.xlsx
+++ b/public/downloads/BajdichWO32018.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -165,6 +167,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
@@ -659,10 +682,10 @@
         <v>250</v>
       </c>
       <c r="N3" s="5">
-        <v>2351.352925777435</v>
+        <v>2351352.925777435</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03222223186353083</v>
+        <v>32.22223186353083</v>
       </c>
       <c r="P3" s="5">
         <v>72973</v>
@@ -709,10 +732,10 @@
         <v>250</v>
       </c>
       <c r="N4" s="5">
-        <v>4648.364782571793</v>
+        <v>4648364.782571793</v>
       </c>
       <c r="O4" s="4">
-        <v>0.0610133723068778</v>
+        <v>61.01337230687781</v>
       </c>
       <c r="P4" s="5">
         <v>76186</v>
@@ -759,10 +782,10 @@
         <v>250</v>
       </c>
       <c r="N5" s="5">
-        <v>12035.47239160538</v>
+        <v>12035472.39160538</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1320663695694748</v>
+        <v>132.0663695694748</v>
       </c>
       <c r="P5" s="5">
         <v>91132</v>
@@ -809,10 +832,10 @@
         <v>250</v>
       </c>
       <c r="N6" s="5">
-        <v>6010.797144174576</v>
+        <v>6010797.144174576</v>
       </c>
       <c r="O6" s="4">
-        <v>0.09078108415656642</v>
+        <v>90.78108415656642</v>
       </c>
       <c r="P6" s="5">
         <v>66212</v>
@@ -859,10 +882,10 @@
         <v>250</v>
       </c>
       <c r="N7" s="5">
-        <v>17547.40323138237</v>
+        <v>17547403.23138237</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2627250072074019</v>
+        <v>262.7250072074019</v>
       </c>
       <c r="P7" s="5">
         <v>66790</v>
@@ -909,10 +932,10 @@
         <v>250</v>
       </c>
       <c r="N8" s="5">
-        <v>1485.19914484024</v>
+        <v>1485199.14484024</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01640850194268556</v>
+        <v>16.40850194268556</v>
       </c>
       <c r="P8" s="5">
         <v>90514</v>
@@ -959,10 +982,10 @@
         <v>250</v>
       </c>
       <c r="N9" s="5">
-        <v>2205.810747623444</v>
+        <v>2205810.747623444</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02895752812801538</v>
+        <v>28.95752812801538</v>
       </c>
       <c r="P9" s="5">
         <v>76174</v>
@@ -1009,10 +1032,10 @@
         <v>250</v>
       </c>
       <c r="N10" s="5">
-        <v>9566.148015022278</v>
+        <v>9566148.015022278</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08221306669951596</v>
+        <v>82.21306669951596</v>
       </c>
       <c r="P10" s="5">
         <v>116358</v>
@@ -1059,10 +1082,10 @@
         <v>250</v>
       </c>
       <c r="N11" s="5">
-        <v>3856.96563076973</v>
+        <v>3856965.63076973</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04403984551969913</v>
+        <v>44.03984551969913</v>
       </c>
       <c r="P11" s="5">
         <v>87579</v>
@@ -1109,10 +1132,10 @@
         <v>250</v>
       </c>
       <c r="N12" s="5">
-        <v>1931.790683746338</v>
+        <v>1931790.683746338</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02395395535731887</v>
+        <v>23.95395535731888</v>
       </c>
       <c r="P12" s="5">
         <v>80646</v>
@@ -1159,10 +1182,10 @@
         <v>250</v>
       </c>
       <c r="N13" s="5">
-        <v>7344.707109212875</v>
+        <v>7344707.109212875</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07554106953977122</v>
+        <v>75.54106953977121</v>
       </c>
       <c r="P13" s="5">
         <v>97228</v>
@@ -1209,10 +1232,10 @@
         <v>250</v>
       </c>
       <c r="N14" s="5">
-        <v>33354.1539850235</v>
+        <v>33354153.9850235</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3620728830332555</v>
+        <v>362.0728830332555</v>
       </c>
       <c r="P14" s="5">
         <v>92120</v>
@@ -1259,10 +1282,10 @@
         <v>250</v>
       </c>
       <c r="N15" s="5">
-        <v>20096.69201540947</v>
+        <v>20096692.01540947</v>
       </c>
       <c r="O15" s="4">
-        <v>0.367190294630273</v>
+        <v>367.190294630273</v>
       </c>
       <c r="P15" s="5">
         <v>54731</v>
@@ -1309,10 +1332,10 @@
         <v>250</v>
       </c>
       <c r="N16" s="5">
-        <v>8584.263179540634</v>
+        <v>8584263.179540634</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09577978443002103</v>
+        <v>95.77978443002102</v>
       </c>
       <c r="P16" s="5">
         <v>89625</v>
@@ -1359,10 +1382,10 @@
         <v>250</v>
       </c>
       <c r="N17" s="5">
-        <v>6899.511126995087</v>
+        <v>6899511.126995087</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1005891607790393</v>
+        <v>100.5891607790393</v>
       </c>
       <c r="P17" s="5">
         <v>68591</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,25 +1497,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8193144637728415</v>
+        <v>0.8563226912936874</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3593144155213926</v>
+        <v>0.6415882051203127</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2839386236491814</v>
+        <v>0.4938521159458953</v>
       </c>
       <c r="E3" s="4">
-        <v>75.75599287333982</v>
+        <v>74.95059928733387</v>
       </c>
       <c r="F3" s="4">
-        <v>71.85362735698291</v>
+        <v>70.25700436774223</v>
       </c>
       <c r="G3" s="5">
         <v>84</v>
@@ -1493,99 +1548,153 @@
         <v>45</v>
       </c>
       <c r="K3" s="5">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3235842289977618</v>
+      </c>
+      <c r="O3" s="5">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7612635596046169</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6333643772397064</v>
+      </c>
+      <c r="R3" s="5">
+        <v>39</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7132720656492071</v>
+        <v>0.7173189709573498</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3469120396328192</v>
+        <v>0.3749906046405282</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3071994977657857</v>
+        <v>0.4257717867630108</v>
       </c>
       <c r="E4" s="4">
-        <v>75.62115322319423</v>
+        <v>73.03045027534824</v>
       </c>
       <c r="F4" s="4">
-        <v>70.4112069883882</v>
+        <v>66.80981676786992</v>
       </c>
       <c r="G4" s="5">
         <v>84</v>
       </c>
       <c r="H4" s="5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I4" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J4" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K4" s="5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.06344742992833372</v>
+      </c>
+      <c r="O4" s="5">
+        <v>33</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6930565078221379</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3829051029026167</v>
+      </c>
+      <c r="R4" s="5">
+        <v>33</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6970865787185646</v>
+        <v>0.7591971297086447</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2917268481385345</v>
+        <v>0.419580530837564</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2331120478179373</v>
+        <v>0.4229548960698667</v>
       </c>
       <c r="E5" s="4">
-        <v>75.5811348929812</v>
+        <v>67.55102040816304</v>
       </c>
       <c r="F5" s="4">
-        <v>71.28185191247897</v>
+        <v>54.06886015168838</v>
       </c>
       <c r="G5" s="5">
         <v>82</v>
       </c>
       <c r="H5" s="5">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="I5" s="5">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J5" s="5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K5" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.05455220343981797</v>
+      </c>
+      <c r="O5" s="5">
+        <v>25</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7857006552908717</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4086700901496005</v>
+      </c>
+      <c r="R5" s="5">
+        <v>25</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.7676083018329148</v>
+        <v>0.7897133051653471</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5276451461445313</v>
+        <v>0.6808467185620759</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4089833982303875</v>
+        <v>0.5764747960760497</v>
       </c>
       <c r="E3" s="4">
-        <v>74.4991091674768</v>
+        <v>74.66107871720108</v>
       </c>
       <c r="F3" s="4">
-        <v>73.25356876531434</v>
+        <v>70.33636944710766</v>
       </c>
       <c r="G3" s="5">
         <v>84</v>
       </c>
       <c r="H3" s="5">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K3" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" s="5">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3525929341419742</v>
+      </c>
+      <c r="O3" s="5">
+        <v>38</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6963382441357299</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.6342761791700572</v>
+      </c>
+      <c r="R3" s="5">
+        <v>38</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7087800048595609</v>
+        <v>0.6771084914610362</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3170065315043826</v>
+        <v>0.494812025943622</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3346461919133358</v>
+        <v>0.4857114120233154</v>
       </c>
       <c r="E4" s="4">
-        <v>73.74635568513101</v>
+        <v>73.37949465500481</v>
       </c>
       <c r="F4" s="4">
-        <v>69.73407371897314</v>
+        <v>67.12488015340378</v>
       </c>
       <c r="G4" s="5">
         <v>84</v>
       </c>
       <c r="H4" s="5">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="I4" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J4" s="5">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="K4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1847199225583903</v>
+      </c>
+      <c r="O4" s="5">
+        <v>33</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6094506941331846</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.5022427071875001</v>
+      </c>
+      <c r="R4" s="5">
+        <v>33</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>1.023473537953685</v>
+        <v>0.6197118445563786</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4211255306349875</v>
+        <v>0.4757570053110596</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3678998723538431</v>
+        <v>0.5102111504753448</v>
       </c>
       <c r="E5" s="4">
-        <v>67.32122117139532</v>
+        <v>69.40393230462924</v>
       </c>
       <c r="F5" s="4">
-        <v>53.29281933759014</v>
+        <v>55.57183390625826</v>
       </c>
       <c r="G5" s="5">
         <v>82</v>
       </c>
       <c r="H5" s="5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I5" s="5">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J5" s="5">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K5" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2638304360723877</v>
+      </c>
+      <c r="O5" s="5">
+        <v>25</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7169141477591463</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4183924505125</v>
+      </c>
+      <c r="R5" s="5">
+        <v>25</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,132 +2097,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5805628584254673</v>
+        <v>0.8193144637728415</v>
       </c>
       <c r="C3" s="4">
-        <v>0.230947748053711</v>
+        <v>0.3593144155213926</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2430055357535807</v>
+        <v>0.2839386236491814</v>
       </c>
       <c r="E3" s="4">
-        <v>77.30442176870774</v>
+        <v>75.75599287333982</v>
       </c>
       <c r="F3" s="4">
-        <v>77.28374347501853</v>
+        <v>71.85362735698291</v>
       </c>
       <c r="G3" s="5">
         <v>84</v>
       </c>
       <c r="H3" s="5">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
+        <v>45</v>
+      </c>
+      <c r="K3" s="5">
+        <v>11</v>
+      </c>
+      <c r="L3" s="5">
         <v>34</v>
       </c>
-      <c r="K3" s="5">
-        <v>6</v>
-      </c>
-      <c r="L3" s="5">
-        <v>27</v>
-      </c>
       <c r="M3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.1505008939308499</v>
+      </c>
+      <c r="O3" s="5">
+        <v>39</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.7579821916770435</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3305141455894199</v>
+      </c>
+      <c r="R3" s="5">
+        <v>39</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4545309691348121</v>
+        <v>0.7132720656492071</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2453546356245349</v>
+        <v>0.3469120396328192</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2449003412749953</v>
+        <v>0.3071994977657857</v>
       </c>
       <c r="E4" s="4">
-        <v>77.33803045027534</v>
+        <v>75.62115322319423</v>
       </c>
       <c r="F4" s="4">
-        <v>75.98300841589422</v>
+        <v>70.4112069883882</v>
       </c>
       <c r="G4" s="5">
         <v>84</v>
       </c>
       <c r="H4" s="5">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="I4" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" s="5">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L4" s="5">
+        <v>32</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1896460993084341</v>
+      </c>
+      <c r="O4" s="5">
         <v>30</v>
       </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="P4" s="4">
+        <v>0.6152218313481917</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.278535777011457</v>
+      </c>
+      <c r="R4" s="5">
+        <v>30</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.9077662959456579</v>
+        <v>0.6970865787185646</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2710823994740126</v>
+        <v>0.2917268481385345</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2158341044014982</v>
+        <v>0.2331120478179373</v>
       </c>
       <c r="E5" s="4">
-        <v>73.06039488966314</v>
+        <v>75.5811348929812</v>
       </c>
       <c r="F5" s="4">
-        <v>64.87723031592857</v>
+        <v>71.28185191247897</v>
       </c>
       <c r="G5" s="5">
         <v>82</v>
       </c>
       <c r="H5" s="5">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I5" s="5">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J5" s="5">
         <v>26</v>
       </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L5" s="5">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.163102235880048</v>
+      </c>
+      <c r="O5" s="5">
+        <v>48</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6359793925417279</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2683571896242865</v>
+      </c>
+      <c r="R5" s="5">
+        <v>48</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2397,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6734832541548664</v>
+        <v>0.7676083018329148</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4428528096920341</v>
+        <v>0.5276451461445313</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4350892336128743</v>
+        <v>0.4089833982303875</v>
       </c>
       <c r="E3" s="4">
-        <v>74.52421444768432</v>
+        <v>74.4991091674768</v>
       </c>
       <c r="F3" s="4">
-        <v>71.1689038031316</v>
+        <v>73.25356876531434</v>
       </c>
       <c r="G3" s="5">
         <v>84</v>
       </c>
       <c r="H3" s="5">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L3" s="5">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3114070307389648</v>
+      </c>
+      <c r="O3" s="5">
+        <v>50</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6896628171270833</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.510338438375625</v>
+      </c>
+      <c r="R3" s="5">
+        <v>50</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7990203854334078</v>
+        <v>0.7087800048595609</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4803391274601799</v>
+        <v>0.3170065315043826</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4698321152991158</v>
+        <v>0.3346461919133358</v>
       </c>
       <c r="E4" s="4">
-        <v>72.26878846776806</v>
+        <v>73.74635568513101</v>
       </c>
       <c r="F4" s="4">
-        <v>66.37597208905903</v>
+        <v>69.73407371897314</v>
       </c>
       <c r="G4" s="5">
         <v>84</v>
       </c>
       <c r="H4" s="5">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I4" s="5">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J4" s="5">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K4" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L4" s="5">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.05486993507717226</v>
+      </c>
+      <c r="O4" s="5">
+        <v>41</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6871692662270888</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3195710603476353</v>
+      </c>
+      <c r="R4" s="5">
+        <v>41</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.8343504465180784</v>
+        <v>1.023473537953685</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3750881852146754</v>
+        <v>0.4211255306349875</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2671059231142519</v>
+        <v>0.3678998723538431</v>
       </c>
       <c r="E5" s="4">
-        <v>67.86875725900113</v>
+        <v>67.32122117139532</v>
       </c>
       <c r="F5" s="4">
-        <v>57.24982266601204</v>
+        <v>53.29281933759014</v>
       </c>
       <c r="G5" s="5">
         <v>82</v>
       </c>
       <c r="H5" s="5">
+        <v>22</v>
+      </c>
+      <c r="I5" s="5">
+        <v>31</v>
+      </c>
+      <c r="J5" s="5">
         <v>29</v>
       </c>
-      <c r="I5" s="5">
-        <v>20</v>
-      </c>
-      <c r="J5" s="5">
-        <v>33</v>
-      </c>
       <c r="K5" s="5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L5" s="5">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2028131159807795</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.136315722335349</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3344511837638817</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.8563839644297898</v>
+        <v>0.5805628584254673</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4607116272857158</v>
+        <v>0.230947748053711</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7527374984964335</v>
+        <v>0.2430055357535807</v>
       </c>
       <c r="E3" s="4">
-        <v>59.5290735341753</v>
+        <v>77.30442176870774</v>
       </c>
       <c r="F3" s="4">
-        <v>59.8451315649307</v>
+        <v>77.28374347501853</v>
       </c>
       <c r="G3" s="5">
         <v>84</v>
       </c>
       <c r="H3" s="5">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="K3" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2462256627156575</v>
+      </c>
+      <c r="O3" s="5">
+        <v>51</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5287599846304564</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1867875543619791</v>
+      </c>
+      <c r="R3" s="5">
+        <v>50</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.5088809367977475</v>
+        <v>0.4545309691348121</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2134790836557741</v>
+        <v>0.2453546356245349</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3517639988278286</v>
+        <v>0.2449003412749953</v>
       </c>
       <c r="E4" s="4">
-        <v>60.04859086491744</v>
+        <v>77.33803045027534</v>
       </c>
       <c r="F4" s="4">
-        <v>58.5277511452004</v>
+        <v>75.98300841589422</v>
       </c>
       <c r="G4" s="5">
         <v>84</v>
       </c>
       <c r="H4" s="5">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I4" s="5">
+        <v>11</v>
+      </c>
+      <c r="J4" s="5">
+        <v>31</v>
+      </c>
+      <c r="K4" s="5">
         <v>1</v>
       </c>
-      <c r="J4" s="5">
-        <v>55</v>
-      </c>
-      <c r="K4" s="5">
-        <v>7</v>
-      </c>
       <c r="L4" s="5">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1796099741922433</v>
+      </c>
+      <c r="O4" s="5">
+        <v>42</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3964793987841464</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1861179508184524</v>
+      </c>
+      <c r="R4" s="5">
+        <v>42</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.5145816882430894</v>
+        <v>0.9077662959456579</v>
       </c>
       <c r="C5" s="4">
-        <v>0.3194012175829308</v>
+        <v>0.2710823994740126</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4902733161533516</v>
+        <v>0.2158341044014982</v>
       </c>
       <c r="E5" s="4">
-        <v>63.80039820806386</v>
+        <v>73.06039488966314</v>
       </c>
       <c r="F5" s="4">
-        <v>62.76081737327433</v>
+        <v>64.87723031592857</v>
       </c>
       <c r="G5" s="5">
         <v>82</v>
       </c>
       <c r="H5" s="5">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J5" s="5">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="K5" s="5">
+        <v>3</v>
+      </c>
+      <c r="L5" s="5">
+        <v>22</v>
+      </c>
+      <c r="M5" s="5">
         <v>1</v>
       </c>
-      <c r="L5" s="5">
+      <c r="N5" s="4">
+        <v>-0.2510586225788509</v>
+      </c>
+      <c r="O5" s="5">
         <v>37</v>
       </c>
-      <c r="M5" s="5">
+      <c r="P5" s="4">
+        <v>0.8050512537768572</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2960305949085784</v>
+      </c>
+      <c r="R5" s="5">
+        <v>37</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,132 +2997,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5050466314307061</v>
+        <v>0.6734832541548664</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4444554877671577</v>
+        <v>0.4428528096920341</v>
       </c>
       <c r="D3" s="4">
-        <v>0.442598117532033</v>
+        <v>0.4350892336128743</v>
       </c>
       <c r="E3" s="4">
-        <v>80.85236475542565</v>
+        <v>74.52421444768432</v>
       </c>
       <c r="F3" s="4">
-        <v>80.63452114626499</v>
+        <v>71.1689038031316</v>
       </c>
       <c r="G3" s="5">
         <v>84</v>
       </c>
       <c r="H3" s="5">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L3" s="5">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3824040934838867</v>
+      </c>
+      <c r="O3" s="5">
+        <v>49</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5784184978776041</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4057815163903062</v>
+      </c>
+      <c r="R3" s="5">
+        <v>49</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6109504058816285</v>
+        <v>0.7990203854334078</v>
       </c>
       <c r="C4" s="4">
-        <v>0.524165047606847</v>
+        <v>0.4803391274601799</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5198516780320289</v>
+        <v>0.4698321152991158</v>
       </c>
       <c r="E4" s="4">
-        <v>81.42614188532589</v>
+        <v>72.26878846776806</v>
       </c>
       <c r="F4" s="4">
-        <v>81.06077554063964</v>
+        <v>66.37597208905903</v>
       </c>
       <c r="G4" s="5">
         <v>84</v>
       </c>
       <c r="H4" s="5">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="I4" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J4" s="5">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="K4" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L4" s="5">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.4780132219372139</v>
+      </c>
+      <c r="O4" s="5">
+        <v>29</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5717699795182292</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3407383947110953</v>
+      </c>
+      <c r="R4" s="5">
+        <v>29</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.977109303218935</v>
+        <v>0.8343504465180784</v>
       </c>
       <c r="C5" s="4">
-        <v>0.7010114499865389</v>
+        <v>0.3750881852146754</v>
       </c>
       <c r="D5" s="4">
-        <v>0.621603990540898</v>
+        <v>0.2671059231142519</v>
       </c>
       <c r="E5" s="4">
-        <v>78.50215696034526</v>
+        <v>67.86875725900113</v>
       </c>
       <c r="F5" s="4">
-        <v>75.84165438969823</v>
+        <v>57.24982266601204</v>
       </c>
       <c r="G5" s="5">
         <v>82</v>
       </c>
       <c r="H5" s="5">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="I5" s="5">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J5" s="5">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M5" s="5">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2205679903456695</v>
+      </c>
+      <c r="O5" s="5">
+        <v>29</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.7553698181605473</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3927624464744351</v>
+      </c>
+      <c r="R5" s="5">
+        <v>29</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3297,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.059787249601226</v>
+        <v>0.8563839644297898</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4666028902291198</v>
+        <v>0.4607116272857158</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6753664561344371</v>
+        <v>0.7527374984964335</v>
       </c>
       <c r="E3" s="4">
-        <v>61.29859086491762</v>
+        <v>59.5290735341753</v>
       </c>
       <c r="F3" s="4">
-        <v>55.07403856397096</v>
+        <v>59.8451315649307</v>
       </c>
       <c r="G3" s="5">
         <v>84</v>
       </c>
       <c r="H3" s="5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L3" s="5">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3174875686502333</v>
+      </c>
+      <c r="O3" s="5">
+        <v>25</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.8898881998966053</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2693074477706768</v>
+      </c>
+      <c r="R3" s="5">
+        <v>25</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7202257319905749</v>
+        <v>0.5088809367977475</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2924276950874443</v>
+        <v>0.2134790836557741</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4284556794780206</v>
+        <v>0.3517639988278286</v>
       </c>
       <c r="E4" s="4">
-        <v>61.30183025591187</v>
+        <v>60.04859086491744</v>
       </c>
       <c r="F4" s="4">
-        <v>52.97565782465101</v>
+        <v>58.5277511452004</v>
       </c>
       <c r="G4" s="5">
         <v>84</v>
       </c>
       <c r="H4" s="5">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K4" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
+        <v>48</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.006125978032834989</v>
+      </c>
+      <c r="O4" s="5">
+        <v>28</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5112747344766674</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2132217890812344</v>
+      </c>
+      <c r="R4" s="5">
+        <v>28</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="B5" s="4">
-        <v>0.4995878947123201</v>
+        <v>0.5145816882430894</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2766934234298347</v>
+        <v>0.3194012175829308</v>
       </c>
       <c r="D5" s="4">
-        <v>0.4927860988365801</v>
+        <v>0.4902733161533516</v>
       </c>
       <c r="E5" s="4">
-        <v>65.30280404844865</v>
+        <v>63.80039820806386</v>
       </c>
       <c r="F5" s="4">
-        <v>58.08588421454578</v>
+        <v>62.76081737327433</v>
       </c>
       <c r="G5" s="5">
         <v>82</v>
       </c>
       <c r="H5" s="5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="I5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K5" s="5">
         <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2878584227649165</v>
+      </c>
+      <c r="O5" s="5">
+        <v>40</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.4879307517275433</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1795628879555499</v>
+      </c>
+      <c r="R5" s="5">
+        <v>40</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,132 +3597,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4771637946259133</v>
+        <v>0.5050466314307061</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3120715721973075</v>
+        <v>0.4444554877671577</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3045087933971005</v>
+        <v>0.442598117532033</v>
       </c>
       <c r="E3" s="4">
-        <v>78.51352445740181</v>
+        <v>80.85236475542565</v>
       </c>
       <c r="F3" s="4">
-        <v>78.4882017684035</v>
+        <v>80.63452114626499</v>
       </c>
       <c r="G3" s="5">
         <v>84</v>
       </c>
       <c r="H3" s="5">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.4423113327220065</v>
+      </c>
+      <c r="O3" s="5">
+        <v>65</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2580806762100517</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1855950306206811</v>
+      </c>
+      <c r="R3" s="5">
+        <v>65</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4618993964231656</v>
+        <v>0.6109504058816285</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3345392344802345</v>
+        <v>0.524165047606847</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3251597963703021</v>
+        <v>0.5198516780320289</v>
       </c>
       <c r="E4" s="4">
-        <v>77.70813087139612</v>
+        <v>81.42614188532589</v>
       </c>
       <c r="F4" s="4">
-        <v>77.05310535847383</v>
+        <v>81.06077554063964</v>
       </c>
       <c r="G4" s="5">
         <v>84</v>
       </c>
       <c r="H4" s="5">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="I4" s="5">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J4" s="5">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.524165047606847</v>
+      </c>
+      <c r="O4" s="5">
+        <v>63</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3061342397836642</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.200337637813655</v>
+      </c>
+      <c r="R4" s="5">
+        <v>63</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.6387635767381266</v>
+        <v>0.977109303218935</v>
       </c>
       <c r="C5" s="4">
-        <v>0.5158156745289293</v>
+        <v>0.7010114499865389</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3902273258733213</v>
+        <v>0.621603990540898</v>
       </c>
       <c r="E5" s="4">
-        <v>78.88169902107181</v>
+        <v>78.50215696034526</v>
       </c>
       <c r="F5" s="4">
-        <v>78.95468434550244</v>
+        <v>75.84165438969823</v>
       </c>
       <c r="G5" s="5">
         <v>82</v>
       </c>
       <c r="H5" s="5">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I5" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J5" s="5">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K5" s="5">
+        <v>2</v>
+      </c>
+      <c r="L5" s="5">
+        <v>12</v>
+      </c>
+      <c r="M5" s="5">
         <v>1</v>
       </c>
-      <c r="L5" s="5">
-        <v>8</v>
-      </c>
-      <c r="M5" s="5">
+      <c r="N5" s="4">
+        <v>-0.7325042241984516</v>
+      </c>
+      <c r="O5" s="5">
+        <v>60</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5136880427669341</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2568027211499225</v>
+      </c>
+      <c r="R5" s="5">
+        <v>60</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1.059787249601226</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4666028902291198</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6753664561344371</v>
+      </c>
+      <c r="E3" s="4">
+        <v>61.29859086491762</v>
+      </c>
+      <c r="F3" s="4">
+        <v>55.07403856397096</v>
+      </c>
+      <c r="G3" s="5">
+        <v>84</v>
+      </c>
+      <c r="H3" s="5">
+        <v>22</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>62</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>61</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2742624511982142</v>
+      </c>
+      <c r="O3" s="5">
+        <v>22</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.9245114717165509</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3834828208875576</v>
+      </c>
+      <c r="R3" s="5">
+        <v>22</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.7202257319905749</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.2924276950874443</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.4284556794780206</v>
+      </c>
+      <c r="E4" s="4">
+        <v>61.30183025591187</v>
+      </c>
+      <c r="F4" s="4">
+        <v>52.97565782465101</v>
+      </c>
+      <c r="G4" s="5">
+        <v>84</v>
+      </c>
+      <c r="H4" s="5">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>60</v>
+      </c>
+      <c r="K4" s="5">
+        <v>6</v>
+      </c>
+      <c r="L4" s="5">
+        <v>54</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1054198903481554</v>
+      </c>
+      <c r="O4" s="5">
+        <v>23</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.7703441937013826</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3085446267055444</v>
+      </c>
+      <c r="R4" s="5">
+        <v>23</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.4995878947123201</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2766934234298347</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.4927860988365801</v>
+      </c>
+      <c r="E5" s="4">
+        <v>65.30280404844865</v>
+      </c>
+      <c r="F5" s="4">
+        <v>58.08588421454578</v>
+      </c>
+      <c r="G5" s="5">
+        <v>82</v>
+      </c>
+      <c r="H5" s="5">
+        <v>34</v>
+      </c>
+      <c r="I5" s="5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="5">
+        <v>43</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>42</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.2210137760088745</v>
+      </c>
+      <c r="O5" s="5">
+        <v>34</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5001991683346537</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2176098189897216</v>
+      </c>
+      <c r="R5" s="5">
+        <v>34</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.4771637946259133</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.3120715721973075</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.3045087933971005</v>
+      </c>
+      <c r="E3" s="4">
+        <v>78.51352445740181</v>
+      </c>
+      <c r="F3" s="4">
+        <v>78.4882017684035</v>
+      </c>
+      <c r="G3" s="5">
+        <v>84</v>
+      </c>
+      <c r="H3" s="5">
+        <v>63</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>21</v>
+      </c>
+      <c r="K3" s="5">
+        <v>4</v>
+      </c>
+      <c r="L3" s="5">
+        <v>17</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.3091929834971735</v>
+      </c>
+      <c r="O3" s="5">
+        <v>63</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2907432700768288</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1358546241829645</v>
+      </c>
+      <c r="R3" s="5">
+        <v>63</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4618993964231656</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3345392344802345</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3251597963703021</v>
+      </c>
+      <c r="E4" s="4">
+        <v>77.70813087139612</v>
+      </c>
+      <c r="F4" s="4">
+        <v>77.05310535847383</v>
+      </c>
+      <c r="G4" s="5">
+        <v>84</v>
+      </c>
+      <c r="H4" s="5">
+        <v>41</v>
+      </c>
+      <c r="I4" s="5">
+        <v>26</v>
+      </c>
+      <c r="J4" s="5">
+        <v>17</v>
+      </c>
+      <c r="K4" s="5">
+        <v>2</v>
+      </c>
+      <c r="L4" s="5">
+        <v>15</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.3332298601460277</v>
+      </c>
+      <c r="O4" s="5">
+        <v>41</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2550256386984032</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1306853675757423</v>
+      </c>
+      <c r="R4" s="5">
+        <v>41</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.6387635767381266</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5158156745289293</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3902273258733213</v>
+      </c>
+      <c r="E5" s="4">
+        <v>78.88169902107181</v>
+      </c>
+      <c r="F5" s="4">
+        <v>78.95468434550244</v>
+      </c>
+      <c r="G5" s="5">
+        <v>82</v>
+      </c>
+      <c r="H5" s="5">
+        <v>69</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="5">
+        <v>9</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>8</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.5158156745289293</v>
+      </c>
+      <c r="O5" s="5">
+        <v>69</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.356657330617101</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2035575050775244</v>
+      </c>
+      <c r="R5" s="5">
+        <v>69</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>40</v>
+      </c>
+      <c r="C3" s="3">
+        <v>18.4</v>
+      </c>
+      <c r="D3" s="3">
+        <v>41.6</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="F3" s="3">
+        <v>38</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.7339799327400526</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.3911263978723223</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.3340228633364558</v>
+      </c>
+      <c r="K3" s="4">
+        <v>72.6791836734694</v>
+      </c>
+      <c r="L3" s="4">
+        <v>65.24908277404887</v>
+      </c>
+      <c r="M3" s="5">
+        <v>250</v>
+      </c>
+      <c r="N3" s="5">
+        <v>2351352.925777435</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.22223186353083</v>
+      </c>
+      <c r="P3" s="5">
+        <v>72973</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3">
+        <v>17.2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>38.8</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="F4" s="3">
+        <v>29.6</v>
+      </c>
+      <c r="G4" s="3">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.112408596344104</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.5324892937982791</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.9150631213069371</v>
+      </c>
+      <c r="K4" s="4">
+        <v>75.86857142857167</v>
+      </c>
+      <c r="L4" s="4">
+        <v>67.76478747203583</v>
+      </c>
+      <c r="M4" s="5">
+        <v>250</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4648364.782571793</v>
+      </c>
+      <c r="O4" s="4">
+        <v>61.01337230687781</v>
+      </c>
+      <c r="P4" s="5">
+        <v>76186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>59.59999999999999</v>
+      </c>
+      <c r="C5" s="3">
+        <v>8.799999999999999</v>
+      </c>
+      <c r="D5" s="3">
+        <v>31.6</v>
+      </c>
+      <c r="E5" s="3">
+        <v>6.4</v>
+      </c>
+      <c r="F5" s="3">
+        <v>25.2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.5472253775552425</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.2250361732834091</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.2112336308704252</v>
+      </c>
+      <c r="K5" s="4">
+        <v>74.54435374149664</v>
+      </c>
+      <c r="L5" s="4">
+        <v>73.99078299776262</v>
+      </c>
+      <c r="M5" s="5">
+        <v>250</v>
+      </c>
+      <c r="N5" s="5">
+        <v>12035472.39160538</v>
+      </c>
+      <c r="O5" s="4">
+        <v>132.0663695694748</v>
+      </c>
+      <c r="P5" s="5">
+        <v>91132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>57.2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="D6" s="3">
+        <v>37.2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F6" s="3">
+        <v>34.8</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.5819232009781042</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.3301960347713934</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.3559588815321849</v>
+      </c>
+      <c r="K6" s="4">
+        <v>74.87142857142868</v>
+      </c>
+      <c r="L6" s="4">
+        <v>71.70299776286485</v>
+      </c>
+      <c r="M6" s="5">
+        <v>250</v>
+      </c>
+      <c r="N6" s="5">
+        <v>6010797.144174576</v>
+      </c>
+      <c r="O6" s="4">
+        <v>90.78108415656642</v>
+      </c>
+      <c r="P6" s="5">
+        <v>66212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>67.2</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="D7" s="3">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>24</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.4240418192187791</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.2519588658587529</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.2478246467956174</v>
+      </c>
+      <c r="K7" s="4">
+        <v>78.63850340136072</v>
+      </c>
+      <c r="L7" s="4">
+        <v>76.29776286353518</v>
+      </c>
+      <c r="M7" s="5">
+        <v>250</v>
+      </c>
+      <c r="N7" s="5">
+        <v>17547403.23138237</v>
+      </c>
+      <c r="O7" s="4">
+        <v>262.7250072074019</v>
+      </c>
+      <c r="P7" s="5">
+        <v>66790</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>38.8</v>
+      </c>
+      <c r="C8" s="3">
+        <v>14.4</v>
+      </c>
+      <c r="D8" s="3">
+        <v>46.8</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>44.4</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.7463613575907955</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.4902456841430403</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.4354300580034021</v>
+      </c>
+      <c r="K8" s="4">
+        <v>71.87836734693869</v>
+      </c>
+      <c r="L8" s="4">
+        <v>63.7890380313201</v>
+      </c>
+      <c r="M8" s="5">
+        <v>250</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1485199.14484024</v>
+      </c>
+      <c r="O8" s="4">
+        <v>16.40850194268556</v>
+      </c>
+      <c r="P8" s="5">
+        <v>90514</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>38.4</v>
+      </c>
+      <c r="C9" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="D9" s="3">
+        <v>49.2</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>47.2</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.6738929237233553</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.5326699521714809</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4671997277007339</v>
+      </c>
+      <c r="K9" s="4">
+        <v>72.50612244897967</v>
+      </c>
+      <c r="L9" s="4">
+        <v>64.41454138702395</v>
+      </c>
+      <c r="M9" s="5">
+        <v>250</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2205810.747623444</v>
+      </c>
+      <c r="O9" s="4">
+        <v>28.95752812801538</v>
+      </c>
+      <c r="P9" s="5">
+        <v>76174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46.8</v>
+      </c>
+      <c r="C10" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="D10" s="3">
+        <v>44.8</v>
+      </c>
+      <c r="E10" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="F10" s="3">
+        <v>34</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.6699977924901657</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.2916860691478362</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.2983352785461126</v>
+      </c>
+      <c r="K10" s="4">
+        <v>75.65333333333324</v>
+      </c>
+      <c r="L10" s="4">
+        <v>71.18143176733726</v>
+      </c>
+      <c r="M10" s="5">
+        <v>250</v>
+      </c>
+      <c r="N10" s="5">
+        <v>9566148.015022278</v>
+      </c>
+      <c r="O10" s="4">
+        <v>82.21306669951596</v>
+      </c>
+      <c r="P10" s="5">
+        <v>116358</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>45.2</v>
+      </c>
+      <c r="C11" s="3">
+        <v>14.8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>40</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4.399999999999999</v>
+      </c>
+      <c r="F11" s="3">
+        <v>35.6</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.8353271369329962</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.406878419786192</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.3496974172639418</v>
+      </c>
+      <c r="K11" s="4">
+        <v>71.89183673469398</v>
+      </c>
+      <c r="L11" s="4">
+        <v>65.52389261744963</v>
+      </c>
+      <c r="M11" s="5">
+        <v>250</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3856965.63076973</v>
+      </c>
+      <c r="O11" s="4">
+        <v>44.03984551969913</v>
+      </c>
+      <c r="P11" s="5">
+        <v>87579</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>51.6</v>
+      </c>
+      <c r="C12" s="3">
+        <v>12.4</v>
+      </c>
+      <c r="D12" s="3">
+        <v>36</v>
+      </c>
+      <c r="E12" s="3">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3">
+        <v>31.6</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.5749372440661157</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.2179028191014834</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.2481207843800727</v>
+      </c>
+      <c r="K12" s="4">
+        <v>75.92367346938801</v>
+      </c>
+      <c r="L12" s="4">
+        <v>72.77736017897114</v>
+      </c>
+      <c r="M12" s="5">
+        <v>250</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1931790.683746338</v>
+      </c>
+      <c r="O12" s="4">
+        <v>23.95395535731888</v>
+      </c>
+      <c r="P12" s="5">
+        <v>80646</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>42.8</v>
+      </c>
+      <c r="C13" s="3">
+        <v>13.2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>44</v>
+      </c>
+      <c r="E13" s="3">
+        <v>5.600000000000001</v>
+      </c>
+      <c r="F13" s="3">
+        <v>38.4</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.6342246287616594</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.3846244738084616</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.3704911064353788</v>
+      </c>
+      <c r="K13" s="4">
+        <v>71.58340136054419</v>
+      </c>
+      <c r="L13" s="4">
+        <v>64.99302013422856</v>
+      </c>
+      <c r="M13" s="5">
+        <v>250</v>
+      </c>
+      <c r="N13" s="5">
+        <v>7344707.109212875</v>
+      </c>
+      <c r="O13" s="4">
+        <v>75.54106953977121</v>
+      </c>
+      <c r="P13" s="5">
+        <v>97228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>37.2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>60.8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>55.60000000000001</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.6308320325160539</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.2138216323307902</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.4260615533704566</v>
+      </c>
+      <c r="K14" s="4">
+        <v>61.10462585034034</v>
+      </c>
+      <c r="L14" s="4">
+        <v>60.35883668903733</v>
+      </c>
+      <c r="M14" s="5">
+        <v>250</v>
+      </c>
+      <c r="N14" s="5">
+        <v>33354153.9850235</v>
+      </c>
+      <c r="O14" s="4">
+        <v>362.0728830332555</v>
+      </c>
+      <c r="P14" s="5">
+        <v>92120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>75.2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="D15" s="3">
+        <v>18</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>16.8</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.3580658898014429</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.2132612310723398</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.2211091672214508</v>
+      </c>
+      <c r="K15" s="4">
+        <v>80.27428571428537</v>
+      </c>
+      <c r="L15" s="4">
+        <v>79.20568232662136</v>
+      </c>
+      <c r="M15" s="5">
+        <v>250</v>
+      </c>
+      <c r="N15" s="5">
+        <v>20096692.01540947</v>
+      </c>
+      <c r="O15" s="4">
+        <v>367.190294630273</v>
+      </c>
+      <c r="P15" s="5">
+        <v>54731</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>31.6</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="D16" s="3">
+        <v>66</v>
+      </c>
+      <c r="E16" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>62.8</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.7335368307941921</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.2902769913848649</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.532665227591543</v>
+      </c>
+      <c r="K16" s="4">
+        <v>62.61306122448975</v>
+      </c>
+      <c r="L16" s="4">
+        <v>55.35686800894808</v>
+      </c>
+      <c r="M16" s="5">
+        <v>250</v>
+      </c>
+      <c r="N16" s="5">
+        <v>8584263.179540634</v>
+      </c>
+      <c r="O16" s="4">
+        <v>95.77978443002102</v>
+      </c>
+      <c r="P16" s="5">
+        <v>89625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>69.19999999999999</v>
+      </c>
+      <c r="C17" s="3">
+        <v>12</v>
+      </c>
+      <c r="D17" s="3">
+        <v>18.8</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="F17" s="3">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.3003619577908871</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.1616324233785051</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.2013789504171916</v>
+      </c>
+      <c r="K17" s="4">
+        <v>78.36367346938793</v>
+      </c>
+      <c r="L17" s="4">
+        <v>78.15901565995478</v>
+      </c>
+      <c r="M17" s="5">
+        <v>250</v>
+      </c>
+      <c r="N17" s="5">
+        <v>6899511.126995087</v>
+      </c>
+      <c r="O17" s="4">
+        <v>100.5891607790393</v>
+      </c>
+      <c r="P17" s="5">
+        <v>68591</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3209,13 +5385,13 @@
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="25" customHeight="1">
@@ -3250,16 +5426,16 @@
         <v>2</v>
       </c>
       <c r="K4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="M4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -3294,16 +5470,16 @@
         <v>0</v>
       </c>
       <c r="K5" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L5" s="5">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="25" customHeight="1">
@@ -3341,13 +5517,13 @@
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="25" customHeight="1">
@@ -3382,16 +5558,16 @@
         <v>3</v>
       </c>
       <c r="K7" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="25" customHeight="1">
@@ -3426,16 +5602,16 @@
         <v>0</v>
       </c>
       <c r="K8" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L8" s="5">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="M8" s="5">
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="25" customHeight="1">
@@ -3479,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="25" customHeight="1">
@@ -3514,16 +5690,16 @@
         <v>0</v>
       </c>
       <c r="K10" s="5">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L10" s="5">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
@@ -3561,13 +5737,13 @@
         <v>0</v>
       </c>
       <c r="L11" s="5">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="25" customHeight="1">
@@ -3602,16 +5778,16 @@
         <v>2</v>
       </c>
       <c r="K12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="5">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M12" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" s="5">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="25" customHeight="1">
@@ -3646,16 +5822,16 @@
         <v>2</v>
       </c>
       <c r="K13" s="5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L13" s="5">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M13" s="5">
         <v>0</v>
       </c>
       <c r="N13" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="25" customHeight="1">
@@ -3690,16 +5866,16 @@
         <v>0</v>
       </c>
       <c r="K14" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="5">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="M14" s="5">
         <v>0</v>
       </c>
       <c r="N14" s="5">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="25" customHeight="1">
@@ -3737,13 +5913,13 @@
         <v>0</v>
       </c>
       <c r="L15" s="5">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="M15" s="5">
         <v>0</v>
       </c>
       <c r="N15" s="5">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="25" customHeight="1">
@@ -3778,16 +5954,16 @@
         <v>0</v>
       </c>
       <c r="K16" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L16" s="5">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="M16" s="5">
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3822,16 +5998,16 @@
         <v>1</v>
       </c>
       <c r="K17" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M17" s="5">
         <v>0</v>
       </c>
       <c r="N17" s="5">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>100</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46</v>
+      </c>
+      <c r="D3" s="5">
+        <v>104</v>
+      </c>
+      <c r="E3" s="5">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5">
+        <v>95</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>9</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>83</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>110</v>
+      </c>
+      <c r="C4" s="5">
+        <v>43</v>
+      </c>
+      <c r="D4" s="5">
+        <v>97</v>
+      </c>
+      <c r="E4" s="5">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5">
+        <v>74</v>
+      </c>
+      <c r="G4" s="5">
+        <v>14</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>7</v>
+      </c>
+      <c r="J4" s="5">
+        <v>2</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>59</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>149</v>
+      </c>
+      <c r="C5" s="5">
+        <v>22</v>
+      </c>
+      <c r="D5" s="5">
+        <v>79</v>
+      </c>
+      <c r="E5" s="5">
+        <v>16</v>
+      </c>
+      <c r="F5" s="5">
+        <v>63</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>16</v>
+      </c>
+      <c r="I5" s="5">
+        <v>16</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>52</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>143</v>
+      </c>
+      <c r="C6" s="5">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5">
+        <v>93</v>
+      </c>
+      <c r="E6" s="5">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5">
+        <v>87</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>6</v>
+      </c>
+      <c r="I6" s="5">
+        <v>6</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>59</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>168</v>
+      </c>
+      <c r="C7" s="5">
+        <v>17</v>
+      </c>
+      <c r="D7" s="5">
+        <v>65</v>
+      </c>
+      <c r="E7" s="5">
+        <v>5</v>
+      </c>
+      <c r="F7" s="5">
+        <v>60</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>5</v>
+      </c>
+      <c r="I7" s="5">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>3</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>40</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>97</v>
+      </c>
+      <c r="C8" s="5">
+        <v>36</v>
+      </c>
+      <c r="D8" s="5">
+        <v>117</v>
+      </c>
+      <c r="E8" s="5">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5">
+        <v>111</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>6</v>
+      </c>
+      <c r="I8" s="5">
+        <v>6</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>93</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>96</v>
+      </c>
+      <c r="C9" s="5">
+        <v>31</v>
+      </c>
+      <c r="D9" s="5">
+        <v>123</v>
+      </c>
+      <c r="E9" s="5">
+        <v>5</v>
+      </c>
+      <c r="F9" s="5">
+        <v>118</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>5</v>
+      </c>
+      <c r="I9" s="5">
+        <v>5</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>93</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>117</v>
+      </c>
+      <c r="C10" s="5">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5">
+        <v>112</v>
+      </c>
+      <c r="E10" s="5">
+        <v>27</v>
+      </c>
+      <c r="F10" s="5">
+        <v>85</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>27</v>
+      </c>
+      <c r="I10" s="5">
+        <v>27</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>69</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>113</v>
+      </c>
+      <c r="C11" s="5">
+        <v>37</v>
+      </c>
+      <c r="D11" s="5">
+        <v>100</v>
+      </c>
+      <c r="E11" s="5">
+        <v>11</v>
+      </c>
+      <c r="F11" s="5">
+        <v>89</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>11</v>
+      </c>
+      <c r="I11" s="5">
+        <v>10</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>72</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>129</v>
+      </c>
+      <c r="C12" s="5">
+        <v>31</v>
+      </c>
+      <c r="D12" s="5">
+        <v>90</v>
+      </c>
+      <c r="E12" s="5">
+        <v>10</v>
+      </c>
+      <c r="F12" s="5">
+        <v>79</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
+        <v>10</v>
+      </c>
+      <c r="I12" s="5">
+        <v>8</v>
+      </c>
+      <c r="J12" s="5">
+        <v>2</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>51</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>107</v>
+      </c>
+      <c r="C13" s="5">
+        <v>33</v>
+      </c>
+      <c r="D13" s="5">
+        <v>110</v>
+      </c>
+      <c r="E13" s="5">
+        <v>14</v>
+      </c>
+      <c r="F13" s="5">
+        <v>96</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>14</v>
+      </c>
+      <c r="I13" s="5">
+        <v>12</v>
+      </c>
+      <c r="J13" s="5">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>67</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>93</v>
+      </c>
+      <c r="C14" s="5">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5">
+        <v>152</v>
+      </c>
+      <c r="E14" s="5">
+        <v>13</v>
+      </c>
+      <c r="F14" s="5">
+        <v>139</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>13</v>
+      </c>
+      <c r="I14" s="5">
+        <v>13</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1</v>
+      </c>
+      <c r="L14" s="5">
+        <v>118</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>188</v>
+      </c>
+      <c r="C15" s="5">
+        <v>17</v>
+      </c>
+      <c r="D15" s="5">
+        <v>45</v>
+      </c>
+      <c r="E15" s="5">
+        <v>3</v>
+      </c>
+      <c r="F15" s="5">
+        <v>42</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>3</v>
+      </c>
+      <c r="I15" s="5">
+        <v>2</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>31</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>79</v>
+      </c>
+      <c r="C16" s="5">
+        <v>6</v>
+      </c>
+      <c r="D16" s="5">
+        <v>165</v>
+      </c>
+      <c r="E16" s="5">
+        <v>8</v>
+      </c>
+      <c r="F16" s="5">
+        <v>157</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>8</v>
+      </c>
+      <c r="I16" s="5">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>1</v>
+      </c>
+      <c r="L16" s="5">
+        <v>122</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>173</v>
+      </c>
+      <c r="C17" s="5">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5">
+        <v>47</v>
+      </c>
+      <c r="E17" s="5">
+        <v>7</v>
+      </c>
+      <c r="F17" s="5">
+        <v>40</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>7</v>
+      </c>
+      <c r="I17" s="5">
+        <v>6</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>28</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6864,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.6199030029295713</v>
@@ -3960,10 +6923,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.1053664696255361</v>
+      </c>
+      <c r="O3" s="5">
+        <v>46</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5887131078780206</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3695402822144477</v>
+      </c>
+      <c r="R3" s="5">
+        <v>46</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.6799866779219782</v>
@@ -4001,10 +6982,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.05434607581583024</v>
+      </c>
+      <c r="O4" s="5">
+        <v>32</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6550213237978739</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4050246815229476</v>
+      </c>
+      <c r="R4" s="5">
+        <v>32</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.8121200632492961</v>
@@ -4042,9 +7041,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2692805075436679</v>
+      </c>
+      <c r="O5" s="5">
+        <v>22</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.9636742795638779</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.4160453180287865</v>
+      </c>
+      <c r="R5" s="5">
+        <v>22</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7164,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>1.12527101978039</v>
@@ -4173,10 +7223,28 @@
       <c r="M3" s="5">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.5482272820004883</v>
+      </c>
+      <c r="O3" s="5">
+        <v>60</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.402189959243385</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.7628375111935831</v>
+      </c>
+      <c r="R3" s="5">
+        <v>48</v>
+      </c>
+      <c r="S3" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.7449468867239815</v>
@@ -4214,17 +7282,33 @@
       <c r="M4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1926026324159532</v>
+      </c>
+      <c r="O4" s="5">
+        <v>47</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6892018519183962</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.38550054599077</v>
+      </c>
+      <c r="R4" s="5">
+        <v>45</v>
+      </c>
+      <c r="S4" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>2.771457587763672</v>
       </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
         <v>3.663874239563405</v>
       </c>
@@ -4255,9 +7339,27 @@
       <c r="M5" s="5">
         <v>17</v>
       </c>
+      <c r="N5" s="4">
+        <v>3.649580050626149</v>
+      </c>
+      <c r="O5" s="5">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
+        <v>1.249088255468736</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2711821888784738</v>
+      </c>
+      <c r="R5" s="5">
+        <v>17</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7462,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5251343409349841</v>
@@ -4386,10 +7521,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.08033545188789769</v>
+      </c>
+      <c r="O3" s="5">
+        <v>57</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.5033107153236767</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2079184158658818</v>
+      </c>
+      <c r="R3" s="5">
+        <v>57</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.620245651494083</v>
@@ -4427,10 +7580,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1912124135141742</v>
+      </c>
+      <c r="O4" s="5">
+        <v>47</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.5344758822041538</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2223776319246312</v>
+      </c>
+      <c r="R4" s="5">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.7808770689543144</v>
@@ -4468,9 +7639,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.3368388705908602</v>
+      </c>
+      <c r="O5" s="5">
+        <v>45</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6052715877618645</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2494953647647783</v>
+      </c>
+      <c r="R5" s="5">
+        <v>45</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7762,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.5182096103040712</v>
@@ -4599,10 +7821,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.3428137525092425</v>
+      </c>
+      <c r="O3" s="5">
+        <v>56</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4530157792164914</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.3889629400677616</v>
+      </c>
+      <c r="R3" s="5">
+        <v>56</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.5226268026774959</v>
@@ -4640,10 +7880,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2303621727908779</v>
+      </c>
+      <c r="O4" s="5">
+        <v>47</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4777181670176355</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3168151323168005</v>
+      </c>
+      <c r="R4" s="5">
+        <v>47</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.8199135288796625</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.003311969636352508</v>
+      </c>
+      <c r="O5" s="5">
+        <v>40</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.8207213263519437</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.263644927740625</v>
+      </c>
+      <c r="R5" s="5">
+        <v>40</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8062,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.341628771864188</v>
@@ -4812,10 +8121,28 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2032872881311035</v>
+      </c>
+      <c r="O3" s="5">
+        <v>64</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3173549440084403</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.239732863401947</v>
+      </c>
+      <c r="R3" s="5">
+        <v>64</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
         <v>0.3833990405134219</v>
@@ -4853,10 +8180,28 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.148057024876452</v>
+      </c>
+      <c r="O4" s="5">
+        <v>57</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3611459724995105</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2440510275</v>
+      </c>
+      <c r="R4" s="5">
+        <v>57</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
         <v>0.6212705186063143</v>
@@ -4894,9 +8239,27 @@
       <c r="M5" s="5">
         <v>1</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.1534086550792419</v>
+      </c>
+      <c r="O5" s="5">
+        <v>47</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5977607050978894</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2781973965754442</v>
+      </c>
+      <c r="R5" s="5">
+        <v>47</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8563226912936874</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6415882051203127</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.4938521159458953</v>
-      </c>
-      <c r="E3" s="4">
-        <v>74.95059928733387</v>
-      </c>
-      <c r="F3" s="4">
-        <v>70.25700436774223</v>
-      </c>
-      <c r="G3" s="5">
-        <v>84</v>
-      </c>
-      <c r="H3" s="5">
-        <v>39</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>45</v>
-      </c>
-      <c r="K3" s="5">
-        <v>2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>43</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.7173189709573498</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.3749906046405282</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4257717867630108</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.03045027534824</v>
-      </c>
-      <c r="F4" s="4">
-        <v>66.80981676786992</v>
-      </c>
-      <c r="G4" s="5">
-        <v>84</v>
-      </c>
-      <c r="H4" s="5">
-        <v>33</v>
-      </c>
-      <c r="I4" s="5">
-        <v>11</v>
-      </c>
-      <c r="J4" s="5">
-        <v>40</v>
-      </c>
-      <c r="K4" s="5">
-        <v>3</v>
-      </c>
-      <c r="L4" s="5">
-        <v>37</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.7591971297086447</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.419580530837564</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4229548960698667</v>
-      </c>
-      <c r="E5" s="4">
-        <v>67.55102040816304</v>
-      </c>
-      <c r="F5" s="4">
-        <v>54.06886015168838</v>
-      </c>
-      <c r="G5" s="5">
-        <v>82</v>
-      </c>
-      <c r="H5" s="5">
-        <v>25</v>
-      </c>
-      <c r="I5" s="5">
-        <v>25</v>
-      </c>
-      <c r="J5" s="5">
-        <v>32</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>31</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.7897133051653471</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.6808467185620759</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5764747960760497</v>
-      </c>
-      <c r="E3" s="4">
-        <v>74.66107871720108</v>
-      </c>
-      <c r="F3" s="4">
-        <v>70.33636944710766</v>
-      </c>
-      <c r="G3" s="5">
-        <v>84</v>
-      </c>
-      <c r="H3" s="5">
-        <v>38</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>46</v>
-      </c>
-      <c r="K3" s="5">
-        <v>3</v>
-      </c>
-      <c r="L3" s="5">
-        <v>43</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.6771084914610362</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.494812025943622</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.4857114120233154</v>
-      </c>
-      <c r="E4" s="4">
-        <v>73.37949465500481</v>
-      </c>
-      <c r="F4" s="4">
-        <v>67.12488015340378</v>
-      </c>
-      <c r="G4" s="5">
-        <v>84</v>
-      </c>
-      <c r="H4" s="5">
-        <v>33</v>
-      </c>
-      <c r="I4" s="5">
-        <v>8</v>
-      </c>
-      <c r="J4" s="5">
-        <v>43</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>43</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.6197118445563786</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4757570053110596</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5102111504753448</v>
-      </c>
-      <c r="E5" s="4">
-        <v>69.40393230462924</v>
-      </c>
-      <c r="F5" s="4">
-        <v>55.57183390625826</v>
-      </c>
-      <c r="G5" s="5">
-        <v>82</v>
-      </c>
-      <c r="H5" s="5">
-        <v>25</v>
-      </c>
-      <c r="I5" s="5">
-        <v>23</v>
-      </c>
-      <c r="J5" s="5">
-        <v>34</v>
-      </c>
-      <c r="K5" s="5">
-        <v>2</v>
-      </c>
-      <c r="L5" s="5">
-        <v>32</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/BajdichWO32018.xlsx
+++ b/public/downloads/BajdichWO32018.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3235842289977618</v>
+        <v>-0.1707117896710626</v>
       </c>
       <c r="O3" s="5">
         <v>39</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7612635596046169</v>
+        <v>0.7981393292680401</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6333643772397064</v>
+        <v>0.6254337880800636</v>
       </c>
       <c r="R3" s="5">
         <v>39</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06344742992833372</v>
+        <v>0.01306432531571655</v>
       </c>
       <c r="O4" s="5">
         <v>33</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6930565078221379</v>
+        <v>0.723375223964745</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3829051029026167</v>
+        <v>0.3741750869034623</v>
       </c>
       <c r="R4" s="5">
         <v>33</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.05455220343981797</v>
+        <v>0.2145031262007553</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7857006552908717</v>
+        <v>0.8724564921709068</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4086700901496005</v>
+        <v>0.3846571666139195</v>
       </c>
       <c r="R5" s="5">
         <v>25</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3525929341419742</v>
+        <v>-0.2501732528015137</v>
       </c>
       <c r="O3" s="5">
         <v>38</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6963382441357299</v>
+        <v>0.7100443241722471</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.6342761791700572</v>
+        <v>0.6291232062047697</v>
       </c>
       <c r="R3" s="5">
         <v>38</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1847199225583903</v>
+        <v>0.01341123246765141</v>
       </c>
       <c r="O4" s="5">
         <v>33</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6094506941331846</v>
+        <v>0.6828561625186014</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5022427071875001</v>
+        <v>0.4944056249597538</v>
       </c>
       <c r="R4" s="5">
         <v>33</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2638304360723877</v>
+        <v>0.2717531913848878</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7169141477591463</v>
+        <v>0.7213586202515245</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.4183924505125</v>
+        <v>0.4180755403</v>
       </c>
       <c r="R5" s="5">
         <v>25</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1505008939308499</v>
+        <v>-0.1632360264151749</v>
       </c>
       <c r="O3" s="5">
         <v>39</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7579821916770435</v>
+        <v>0.7543435823958076</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3305141455894199</v>
+        <v>0.3301876037308475</v>
       </c>
       <c r="R3" s="5">
         <v>39</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1896460993084341</v>
+        <v>-0.1853889631387785</v>
       </c>
       <c r="O4" s="5">
         <v>30</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6152218313481917</v>
+        <v>0.6168435975080605</v>
       </c>
       <c r="Q4" s="4">
         <v>0.278535777011457</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.163102235880048</v>
+        <v>-0.1262296430158609</v>
       </c>
       <c r="O5" s="5">
         <v>48</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6359793925417279</v>
+        <v>0.6454521276878536</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2683571896242865</v>
+        <v>0.2666328158023337</v>
       </c>
       <c r="R5" s="5">
         <v>48</v>
@@ -2457,16 +2457,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3114070307389648</v>
+        <v>-0.1883512620483399</v>
       </c>
       <c r="O3" s="5">
         <v>50</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6896628171270833</v>
+        <v>0.7026883961216518</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.510338438375625</v>
+        <v>0.4974799299671875</v>
       </c>
       <c r="R3" s="5">
         <v>50</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05486993507717226</v>
+        <v>0.00260172394531244</v>
       </c>
       <c r="O4" s="5">
         <v>41</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6871692662270888</v>
+        <v>0.7098330835993304</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3195710603476353</v>
+        <v>0.3169430748227897</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2028131159807795</v>
+        <v>0.2593429059204102</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>1.136315722335349</v>
+        <v>1.172462790616425</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3344511837638817</v>
+        <v>0.3252871547833807</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -2757,16 +2757,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2462256627156575</v>
+        <v>-0.1742401237573241</v>
       </c>
       <c r="O3" s="5">
         <v>51</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5287599846304564</v>
+        <v>0.5230459759263394</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1867875543619791</v>
+        <v>0.1722132065953125</v>
       </c>
       <c r="R3" s="5">
         <v>50</v>
@@ -2816,13 +2816,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1796099741922433</v>
+        <v>-0.1784709661621093</v>
       </c>
       <c r="O4" s="5">
         <v>42</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3964793987841464</v>
+        <v>0.3965878757393974</v>
       </c>
       <c r="Q4" s="4">
         <v>0.1861179508184524</v>
@@ -2875,22 +2875,22 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2510586225788509</v>
+        <v>-0.2124079919897461</v>
       </c>
       <c r="O5" s="5">
         <v>37</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8050512537768572</v>
+        <v>0.8158019972170349</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2960305949085784</v>
+        <v>0.2453582429036459</v>
       </c>
       <c r="R5" s="5">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3824040934838867</v>
+        <v>-0.2054145248120118</v>
       </c>
       <c r="O3" s="5">
         <v>49</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5784184978776041</v>
+        <v>0.5913062703924851</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4057815163903062</v>
+        <v>0.3832699788376914</v>
       </c>
       <c r="R3" s="5">
         <v>49</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.4780132219372139</v>
+        <v>-0.3295800999194336</v>
       </c>
       <c r="O4" s="5">
         <v>29</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5717699795182292</v>
+        <v>0.5919774174423363</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3407383947110953</v>
+        <v>0.2988118474865302</v>
       </c>
       <c r="R4" s="5">
         <v>29</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2205679903456695</v>
+        <v>-0.08734270738769556</v>
       </c>
       <c r="O5" s="5">
         <v>29</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7553698181605473</v>
+        <v>0.7975055065034299</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.3927624464744351</v>
+        <v>0.3719868190247844</v>
       </c>
       <c r="R5" s="5">
         <v>29</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3174875686502333</v>
+        <v>0.4007364811459335</v>
       </c>
       <c r="O3" s="5">
         <v>25</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8898881998966053</v>
+        <v>0.9097396718316227</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2693074477706768</v>
+        <v>0.2527594809766353</v>
       </c>
       <c r="R3" s="5">
         <v>25</v>
@@ -3416,13 +3416,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.006125978032834989</v>
+        <v>0.01212997628970747</v>
       </c>
       <c r="O4" s="5">
         <v>28</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5112747344766674</v>
+        <v>0.5137049242473063</v>
       </c>
       <c r="Q4" s="4">
         <v>0.2132217890812344</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2878584227649165</v>
+        <v>0.2945563180508335</v>
       </c>
       <c r="O5" s="5">
         <v>40</v>
       </c>
       <c r="P5" s="4">
-        <v>0.4879307517275433</v>
+        <v>0.4892916394903009</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1795628879555499</v>
+        <v>0.1793386549905401</v>
       </c>
       <c r="R5" s="5">
         <v>40</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4423113327220065</v>
+        <v>-0.4317617578109743</v>
       </c>
       <c r="O3" s="5">
         <v>65</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2580806762100517</v>
+        <v>0.2580125403373287</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1855950306206811</v>
+        <v>0.1853446769557617</v>
       </c>
       <c r="R3" s="5">
         <v>65</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.524165047606847</v>
+        <v>-0.4704069576777135</v>
       </c>
       <c r="O4" s="5">
         <v>63</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3061342397836642</v>
+        <v>0.3047358417850083</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.200337637813655</v>
+        <v>0.1959131981045361</v>
       </c>
       <c r="R4" s="5">
         <v>63</v>
@@ -3775,16 +3775,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.7325042241984516</v>
+        <v>-0.6793684976427654</v>
       </c>
       <c r="O5" s="5">
         <v>60</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5136880427669341</v>
+        <v>0.5147217140411952</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2568027211499225</v>
+        <v>0.2529018325691771</v>
       </c>
       <c r="R5" s="5">
         <v>60</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2742624511982142</v>
+        <v>-0.3418896700302184</v>
       </c>
       <c r="O3" s="5">
         <v>22</v>
       </c>
       <c r="P3" s="4">
-        <v>0.9245114717165509</v>
+        <v>0.8978941841985895</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3834828208875576</v>
+        <v>0.3802200413928009</v>
       </c>
       <c r="R3" s="5">
         <v>22</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1054198903481554</v>
+        <v>0.02185597678443379</v>
       </c>
       <c r="O4" s="5">
         <v>23</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7703441937013826</v>
+        <v>0.7287113078506651</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3085446267055444</v>
+        <v>0.2903624656818672</v>
       </c>
       <c r="R4" s="5">
         <v>23</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2210137760088745</v>
+        <v>0.1719164211654487</v>
       </c>
       <c r="O5" s="5">
         <v>34</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5001991683346537</v>
+        <v>0.4907157743114864</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2176098189897216</v>
+        <v>0.2149546618693761</v>
       </c>
       <c r="R5" s="5">
         <v>34</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3091929834971735</v>
+        <v>-0.3044554326873214</v>
       </c>
       <c r="O3" s="5">
         <v>63</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2907432700768288</v>
+        <v>0.2912343437522567</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1358546241829645</v>
+        <v>0.1356821976722911</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3332298601460277</v>
+        <v>-0.3180975641010284</v>
       </c>
       <c r="O4" s="5">
         <v>41</v>
       </c>
       <c r="P4" s="4">
-        <v>0.2550256386984032</v>
+        <v>0.2575046802549252</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1306853675757423</v>
+        <v>0.1294900128923974</v>
       </c>
       <c r="R4" s="5">
         <v>41</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5158156745289293</v>
+        <v>-0.4669886254331406</v>
       </c>
       <c r="O5" s="5">
         <v>69</v>
       </c>
       <c r="P5" s="4">
-        <v>0.356657330617101</v>
+        <v>0.3501452499649657</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2035575050775244</v>
+        <v>0.1979414258574123</v>
       </c>
       <c r="R5" s="5">
         <v>69</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.7339799327400526</v>
+        <v>0.7278204754572852</v>
       </c>
       <c r="I3" s="4">
-        <v>0.3911263978723223</v>
+        <v>0.3905922237326233</v>
       </c>
       <c r="J3" s="4">
-        <v>0.3340228633364558</v>
+        <v>0.3400870363569628</v>
       </c>
       <c r="K3" s="4">
         <v>72.6791836734694</v>
@@ -4553,13 +4553,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="3">
-        <v>44</v>
+        <v>45.2</v>
       </c>
       <c r="C4" s="3">
         <v>17.2</v>
       </c>
       <c r="D4" s="3">
-        <v>38.8</v>
+        <v>37.6</v>
       </c>
       <c r="E4" s="3">
         <v>3.6</v>
@@ -4568,16 +4568,16 @@
         <v>29.6</v>
       </c>
       <c r="G4" s="3">
-        <v>5.600000000000001</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="H4" s="4">
-        <v>1.112408596344104</v>
+        <v>1.030418984107852</v>
       </c>
       <c r="I4" s="4">
-        <v>0.5324892937982791</v>
+        <v>0.3805501878610257</v>
       </c>
       <c r="J4" s="4">
-        <v>0.9150631213069371</v>
+        <v>0.8473934809526661</v>
       </c>
       <c r="K4" s="4">
         <v>75.86857142857167</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.5472253775552425</v>
+        <v>0.5504670622168183</v>
       </c>
       <c r="I5" s="4">
-        <v>0.2250361732834091</v>
+        <v>0.2240891117161738</v>
       </c>
       <c r="J5" s="4">
-        <v>0.2112336308704252</v>
+        <v>0.2060658206999772</v>
       </c>
       <c r="K5" s="4">
         <v>74.54435374149664</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.5819232009781042</v>
+        <v>0.5975164553440625</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3301960347713934</v>
+        <v>0.3094738659172858</v>
       </c>
       <c r="J6" s="4">
-        <v>0.3559588815321849</v>
+        <v>0.3332274403497656</v>
       </c>
       <c r="K6" s="4">
         <v>74.87142857142868</v>
@@ -4703,13 +4703,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>67.2</v>
+        <v>66.8</v>
       </c>
       <c r="C7" s="3">
         <v>6.800000000000001</v>
       </c>
       <c r="D7" s="3">
-        <v>26</v>
+        <v>26.4</v>
       </c>
       <c r="E7" s="3">
         <v>2</v>
@@ -4718,16 +4718,16 @@
         <v>24</v>
       </c>
       <c r="G7" s="3">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="H7" s="4">
-        <v>0.4240418192187791</v>
+        <v>0.4303591261153125</v>
       </c>
       <c r="I7" s="4">
-        <v>0.2519588658587529</v>
+        <v>0.2266498816396894</v>
       </c>
       <c r="J7" s="4">
-        <v>0.2478246467956174</v>
+        <v>0.2383309679984375</v>
       </c>
       <c r="K7" s="4">
         <v>78.63850340136072</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.7463613575907955</v>
+        <v>0.7973946193182733</v>
       </c>
       <c r="I8" s="4">
-        <v>0.4902456841430403</v>
+        <v>0.4778981934874714</v>
       </c>
       <c r="J8" s="4">
-        <v>0.4354300580034021</v>
+        <v>0.4035792353796453</v>
       </c>
       <c r="K8" s="4">
         <v>71.87836734693869</v>
@@ -4821,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.6738929237233553</v>
+        <v>0.704620190970625</v>
       </c>
       <c r="I9" s="4">
-        <v>0.5326699521714809</v>
+        <v>0.5278537079890951</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4671997277007339</v>
+        <v>0.4627034217369727</v>
       </c>
       <c r="K9" s="4">
         <v>72.50612244897967</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.6699977924901657</v>
+        <v>0.6724271903293157</v>
       </c>
       <c r="I10" s="4">
-        <v>0.2916860691478362</v>
+        <v>0.2908697864475109</v>
       </c>
       <c r="J10" s="4">
-        <v>0.2983352785461126</v>
+        <v>0.2951404588293153</v>
       </c>
       <c r="K10" s="4">
         <v>75.65333333333324</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.8353271369329962</v>
+        <v>0.8591750125084375</v>
       </c>
       <c r="I11" s="4">
-        <v>0.406878419786192</v>
+        <v>0.3984511501887445</v>
       </c>
       <c r="J11" s="4">
-        <v>0.3496974172639418</v>
+        <v>0.3327202452782617</v>
       </c>
       <c r="K11" s="4">
         <v>71.89183673469398</v>
@@ -4953,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>51.6</v>
+        <v>51.2</v>
       </c>
       <c r="C12" s="3">
         <v>12.4</v>
       </c>
       <c r="D12" s="3">
-        <v>36</v>
+        <v>36.4</v>
       </c>
       <c r="E12" s="3">
         <v>4</v>
@@ -4968,16 +4968,16 @@
         <v>31.6</v>
       </c>
       <c r="G12" s="3">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H12" s="4">
-        <v>0.5749372440661157</v>
+        <v>0.576580029246875</v>
       </c>
       <c r="I12" s="4">
-        <v>0.2179028191014834</v>
+        <v>0.197347742255249</v>
       </c>
       <c r="J12" s="4">
-        <v>0.2481207843800727</v>
+        <v>0.233464979274414</v>
       </c>
       <c r="K12" s="4">
         <v>75.92367346938801</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.6342246287616594</v>
+        <v>0.659165125245625</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3846244738084616</v>
+        <v>0.3573214045969627</v>
       </c>
       <c r="J13" s="4">
-        <v>0.3704911064353788</v>
+        <v>0.3400085037737842</v>
       </c>
       <c r="K13" s="4">
         <v>71.58340136054419</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.6308320325160539</v>
+        <v>0.6387650420353389</v>
       </c>
       <c r="I14" s="4">
-        <v>0.2138216323307902</v>
+        <v>0.209276809874323</v>
       </c>
       <c r="J14" s="4">
-        <v>0.4260615533704566</v>
+        <v>0.417424058315093</v>
       </c>
       <c r="K14" s="4">
         <v>61.10462585034034</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.3580658898014429</v>
+        <v>0.3579121785986172</v>
       </c>
       <c r="I15" s="4">
-        <v>0.2132612310723398</v>
+        <v>0.2104470501960687</v>
       </c>
       <c r="J15" s="4">
-        <v>0.2211091672214508</v>
+        <v>0.2147728303557077</v>
       </c>
       <c r="K15" s="4">
         <v>80.27428571428537</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.7335368307941921</v>
+        <v>0.7074942193027171</v>
       </c>
       <c r="I16" s="4">
-        <v>0.2902769913848649</v>
+        <v>0.2829321028466247</v>
       </c>
       <c r="J16" s="4">
-        <v>0.532665227591543</v>
+        <v>0.5449598155424228</v>
       </c>
       <c r="K16" s="4">
         <v>62.61306122448975</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.3003619577908871</v>
+        <v>0.2992239540549219</v>
       </c>
       <c r="I17" s="4">
-        <v>0.1616324233785051</v>
+        <v>0.1590464009601392</v>
       </c>
       <c r="J17" s="4">
-        <v>0.2013789504171916</v>
+        <v>0.192724326431128</v>
       </c>
       <c r="K17" s="4">
         <v>78.36367346938793</v>
@@ -6154,13 +6154,13 @@
         <v>18</v>
       </c>
       <c r="B4" s="5">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C4" s="5">
         <v>43</v>
       </c>
       <c r="D4" s="5">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E4" s="5">
         <v>9</v>
@@ -6169,7 +6169,7 @@
         <v>74</v>
       </c>
       <c r="G4" s="5">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="5">
         <v>9</v>
@@ -6286,13 +6286,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C7" s="5">
         <v>17</v>
       </c>
       <c r="D7" s="5">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7" s="5">
         <v>5</v>
@@ -6301,7 +6301,7 @@
         <v>60</v>
       </c>
       <c r="G7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="5">
         <v>5</v>
@@ -6506,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C12" s="5">
         <v>31</v>
       </c>
       <c r="D12" s="5">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" s="5">
         <v>10</v>
@@ -6521,7 +6521,7 @@
         <v>79</v>
       </c>
       <c r="G12" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="5">
         <v>10</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1053664696255361</v>
+        <v>-0.08241933961547865</v>
       </c>
       <c r="O3" s="5">
         <v>46</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5887131078780206</v>
+        <v>0.5929815478397332</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3695402822144477</v>
+        <v>0.3685510545900295</v>
       </c>
       <c r="R3" s="5">
         <v>46</v>
@@ -6983,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.05434607581583024</v>
+        <v>-0.038495438987732</v>
       </c>
       <c r="O4" s="5">
         <v>32</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6550213237978739</v>
+        <v>0.6617202521617417</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4050246815229476</v>
+        <v>0.4047774020464898</v>
       </c>
       <c r="R4" s="5">
         <v>32</v>
@@ -7042,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2692805075436679</v>
+        <v>0.2253318779000857</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.9636742795638779</v>
+        <v>0.9336605812707001</v>
       </c>
       <c r="Q5" s="4">
         <v>0.4160453180287865</v>
@@ -7224,22 +7224,22 @@
         <v>9</v>
       </c>
       <c r="N3" s="4">
-        <v>0.5482272820004883</v>
+        <v>-0.1090686960937499</v>
       </c>
       <c r="O3" s="5">
         <v>60</v>
       </c>
       <c r="P3" s="4">
-        <v>1.402189959243385</v>
+        <v>1.101448711320801</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.7628375111935831</v>
+        <v>0.4194817067403876</v>
       </c>
       <c r="R3" s="5">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="S3" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
@@ -7283,16 +7283,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1926026324159532</v>
+        <v>-0.1374453479687499</v>
       </c>
       <c r="O4" s="5">
         <v>47</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6892018519183962</v>
+        <v>0.6994344397895741</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.38550054599077</v>
+        <v>0.3823945825938586</v>
       </c>
       <c r="R4" s="5">
         <v>45</v>
@@ -7340,16 +7340,16 @@
         <v>17</v>
       </c>
       <c r="N5" s="4">
-        <v>3.649580050626149</v>
+        <v>3.7272135153125</v>
       </c>
       <c r="O5" s="5">
         <v>17</v>
       </c>
       <c r="P5" s="4">
-        <v>1.249088255468736</v>
+        <v>1.296714162605993</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2711821888784738</v>
+        <v>0.2588734098713236</v>
       </c>
       <c r="R5" s="5">
         <v>17</v>
@@ -7522,16 +7522,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08033545188789769</v>
+        <v>-0.06059935344120015</v>
       </c>
       <c r="O3" s="5">
         <v>57</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5033107153236767</v>
+        <v>0.5064170737713715</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2079184158658818</v>
+        <v>0.2073024971449327</v>
       </c>
       <c r="R3" s="5">
         <v>57</v>
@@ -7581,16 +7581,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1912124135141742</v>
+        <v>-0.1881183898900604</v>
       </c>
       <c r="O4" s="5">
         <v>47</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5344758822041538</v>
+        <v>0.5352225002135444</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2223776319246312</v>
+        <v>0.2221979163806781</v>
       </c>
       <c r="R4" s="5">
         <v>47</v>
@@ -7640,16 +7640,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3368388705908602</v>
+        <v>-0.3043020127887344</v>
       </c>
       <c r="O5" s="5">
         <v>45</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6052715877618645</v>
+        <v>0.6112078212130689</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2494953647647783</v>
+        <v>0.2473274053012637</v>
       </c>
       <c r="R5" s="5">
         <v>45</v>
@@ -7822,16 +7822,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3428137525092425</v>
+        <v>-0.2030528113415526</v>
       </c>
       <c r="O3" s="5">
         <v>56</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4530157792164914</v>
+        <v>0.4534796998000373</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.3889629400677616</v>
+        <v>0.3798870335560826</v>
       </c>
       <c r="R3" s="5">
         <v>56</v>
@@ -7881,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2303621727908779</v>
+        <v>-0.1007701444830322</v>
       </c>
       <c r="O4" s="5">
         <v>47</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4777181670176355</v>
+        <v>0.4881173001190476</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3168151323168005</v>
+        <v>0.2862258231781915</v>
       </c>
       <c r="R4" s="5">
         <v>47</v>
@@ -7940,16 +7940,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.003311969636352508</v>
+        <v>0.124394476362915</v>
       </c>
       <c r="O5" s="5">
         <v>40</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8207213263519437</v>
+        <v>0.8571337297903963</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.263644927740625</v>
+        <v>0.2382118814414063</v>
       </c>
       <c r="R5" s="5">
         <v>40</v>
@@ -8122,16 +8122,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2032872881311035</v>
+        <v>-0.1276076482299805</v>
       </c>
       <c r="O3" s="5">
         <v>64</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3173549440084403</v>
+        <v>0.3140498830505952</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.239732863401947</v>
+        <v>0.2331407550842285</v>
       </c>
       <c r="R3" s="5">
         <v>64</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.148057024876452</v>
+        <v>-0.08942389990112298</v>
       </c>
       <c r="O4" s="5">
         <v>57</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3611459724995105</v>
+        <v>0.3615389979557292</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2440510275</v>
+        <v>0.2333065788569079</v>
       </c>
       <c r="R4" s="5">
         <v>57</v>
@@ -8240,22 +8240,22 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.1534086550792419</v>
+        <v>-0.003761158912353402</v>
       </c>
       <c r="O5" s="5">
         <v>47</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5977607050978894</v>
+        <v>0.6200038478572789</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.2781973965754442</v>
+        <v>0.209370585078125</v>
       </c>
       <c r="R5" s="5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
